--- a/Assets/DataTables/Datas/__tables__.xlsx
+++ b/Assets/DataTables/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my projects\MiniProject\Assets\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F895FD6A-049E-4B55-A7A4-0C8F4A326E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36636E02-D507-4E24-80C8-67C895693D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="26745" windowHeight="8145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -136,6 +136,18 @@
   </si>
   <si>
     <t>WeaponInfo.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TBItemInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemInfo.xlsx</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -491,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -633,6 +645,20 @@
         <v>35</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
